--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_BCB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_BCB.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro (14.4 min)</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro (14.4 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro (8.3 net)</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro (8.3 net)</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro</t>
         </is>
       </c>
       <c r="D4" t="n">
